--- a/output/cleaned_売上データ_202610.xlsx
+++ b/output/cleaned_売上データ_202610.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,33 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>商品コード</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>売上日</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>金額</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>エラー内容</t>
         </is>
       </c>
     </row>
@@ -470,13 +453,12 @@
           <t>りんご</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>46296</v>
       </c>
       <c r="D2" t="n">
         <v>1200</v>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,13 +471,12 @@
           <t>みかん</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="D3" t="n">
         <v>800</v>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -508,13 +489,12 @@
           <t>バナナ</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>46298</v>
       </c>
       <c r="D4" t="n">
         <v>1500</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -527,13 +507,12 @@
           <t>もも</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>46301</v>
       </c>
       <c r="D5" t="n">
         <v>3000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -546,13 +525,12 @@
           <t>メロン</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>46302</v>
       </c>
       <c r="D6" t="n">
         <v>4500</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,13 +543,12 @@
           <t>りんご</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>46305</v>
       </c>
       <c r="D7" t="n">
         <v>1250</v>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
